--- a/data/trans_orig/IP09B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>5958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>10795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22454</t>
+          <t>22755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26449</t>
+          <t>25890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37578</t>
+          <t>37081</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42525</t>
+          <t>43227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56907</t>
+          <t>57376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13875</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>37929</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14673</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>20969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>81,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15512</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>29982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60804</t>
+          <t>61351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99940</t>
+          <t>99351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>33145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36267</t>
+          <t>36856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54560</t>
+          <t>54400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,94%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10091</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>72,41%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14206</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,79%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>40872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>36280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49525</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69477</t>
+          <t>69449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86430</t>
+          <t>86964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>13384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35009</t>
+          <t>34475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>51990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14737</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26071</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18839</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>52,19%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46455</t>
+          <t>46450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60424</t>
+          <t>59996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>68499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103352</t>
+          <t>103227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125068</t>
+          <t>124300</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,75%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21818</t>
+          <t>22246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35787</t>
+          <t>35792</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>30056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46743</t>
+          <t>45959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55730</t>
+          <t>56498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77446</t>
+          <t>77571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,9%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3633</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>82,24%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27598</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32968</t>
+          <t>33382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46355</t>
+          <t>47382</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>22210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36624</t>
+          <t>36210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>13751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20490</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>23760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47336</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62952</t>
+          <t>63783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>15867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>26513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>27687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35618</t>
+          <t>34787</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51234</t>
+          <t>51137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24124</t>
+          <t>24702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>37344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53626</t>
+          <t>54912</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65039</t>
+          <t>64881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83599</t>
+          <t>84052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12191</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29773</t>
+          <t>28473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19791</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13656</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19456</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17496</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53707</t>
+          <t>53764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58373</t>
+          <t>58136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79100</t>
+          <t>79103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105685</t>
+          <t>105698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128287</t>
+          <t>130081</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22120</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>40893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34291</t>
+          <t>32497</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>56880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/IP09B01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP09B01-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5258</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2457</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7216</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7208</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>67,25%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8862</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5958</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4540</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2560</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5361</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4878</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>32,75%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4409</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10367</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>7818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10367</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>31834</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26429</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37777</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18502</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14074</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22755</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14012</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22544</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>62,29%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,61%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>31834</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>25890</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>37081</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>61,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43227</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57376</t>
+          <t>57104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19619</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13676</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>25024</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11201</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6948</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15629</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7159</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15691</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>37,71%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19619</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>14372</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>25563</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>38,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>23780</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37929</t>
+          <t>37987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>51453</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>51453</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>51453</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>29703</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>29703</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>29703</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>51453</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>51453</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>51453</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14213</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10594</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16980</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>86,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11991</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8130</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14898</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7977</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14882</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>69,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14213</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10682</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16971</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20969</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5457</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>13,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2298</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9066</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2314</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9219</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>30,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5457</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2699</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8988</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6046</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>15699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19670</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17196</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>17196</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>17196</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54908</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>47648</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61161</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>58,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>75,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>35751</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29982</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>41303</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>29720</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>40835</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>65,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>54,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>54908</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>48345</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61351</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81807</t>
+          <t>81973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>100480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26582</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20329</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33842</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>41,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18966</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13414</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>24735</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13882</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>24997</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>34,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>45,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>26582</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20139</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>33145</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>35727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54400</t>
+          <t>54234</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81490</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>54717</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>54717</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>54717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81490</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6844</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9536</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7350</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4653</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10089</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3960</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9917</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>57,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6844</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3746</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9435</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>17844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4707</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7649</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>66,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>5396</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8093</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>42,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4707</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2116</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7805</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,75%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11551</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>12746</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>11551</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42834</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>36298</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48995</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>54,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>35571</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30164</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>40872</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>28995</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>40668</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>65,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>55,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>75,33%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>42834</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36280</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>49280</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>63,76%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69449</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>87016</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24349</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18188</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30885</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>45,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>18685</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13384</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24092</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>13588</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>25261</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>34,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>24,67%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>44,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>24349</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>17903</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>30903</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34475</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51990</t>
+          <t>51732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67183</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67183</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67183</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54256</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>54256</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>54256</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>67183</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>67183</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>67183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11060</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7131</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14810</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>10627</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7445</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13256</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7251</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13240</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>69,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11060</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7104</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14624</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,8%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,5%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8761</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5011</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>12690</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>4613</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7795</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7989</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>30,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>13,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>51,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8761</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5197</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12717</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>44,2%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>9291</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>18516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19821</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>19821</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19821</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15240</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19821</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>19821</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19821</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>60738</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>53340</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69245</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>53548</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46450</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59996</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45792</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>60211</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>65,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>56,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>72,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>60738</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>52596</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>68499</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>61,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103227</t>
+          <t>102905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124300</t>
+          <t>124602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,92%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37817</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29310</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>45215</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28694</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22246</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35792</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>22031</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>34,89%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>37817</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>30056</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>45959</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56498</t>
+          <t>56196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77571</t>
+          <t>77893</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>98555</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>82242</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>82242</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>98555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2844</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4018</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4006</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,92%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -4047,67 +4047,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,77%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>1605</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3549</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,08%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2129</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,77%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5939</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>4449</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22763</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17759</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27691</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>59,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>46,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>17059</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12502</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22066</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>12148</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21506</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>54,89%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22763</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17787</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27400</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>59,1%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33382</t>
+          <t>33413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47382</t>
+          <t>46944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -4390,67 +4390,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>15752</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10824</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>20756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>40,9%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>53,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>14018</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9011</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18575</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9571</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18929</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>45,11%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>59,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>15752</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11115</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>20728</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>40,9%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36210</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>38515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31077</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>38515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4620,67 +4620,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>5913</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3329</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8649</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,2%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>85,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>6112</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3442</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8885</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8893</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5913</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8108</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,2%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15960</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6830</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,23%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>5485</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8155</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>8175</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>47,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4246</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2051</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>6927</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,8%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,11%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10159</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29320</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23419</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35223</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>45,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>26016</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20610</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>31256</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20224</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31287</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>55,21%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>29320</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>23760</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>35233</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>56,99%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47433</t>
+          <t>46415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63783</t>
+          <t>62759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22127</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16224</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28028</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>54,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>21107</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>15867</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26513</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15836</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26899</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>56,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>22127</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>16214</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27687</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34787</t>
+          <t>35811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51137</t>
+          <t>52155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>47123</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,74 +5532,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6883</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3973</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8773</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8041</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4067</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3097</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1049</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>70,67%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7486</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4236</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9469</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>68,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15527</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>12406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2781</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1341</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5364</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>29,33%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,18%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3422</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1439</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>6672</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9432</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9664</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9382</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10908</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40219</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>32466</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48274</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>67,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>54,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29125</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24702</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>32757</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>77,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54912</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>74096</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64881</t>
+          <t>60078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84052</t>
+          <t>78058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19208</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11153</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26961</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>45,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>8448</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4816</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12871</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28473</t>
+          <t>13350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19338</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38509</t>
+          <t>36835</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,01%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59427</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>37573</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65817</t>
+          <t>37486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>103390</t>
+          <t>96913</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15139</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10939</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17840</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>55,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>90,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10959</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7253</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13802</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>66,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>7613</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31724</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8840</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5634</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2791</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9340</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11873</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16593</t>
+          <t>19779</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22304</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38897</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62241</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>53751</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70273</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>60,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>79,07%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>48125</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>41701</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>53764</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>75,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>84,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58136</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>48108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>116648</t>
+          <t>105380</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105698</t>
+          <t>94707</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130081</t>
+          <t>115901</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>78,34%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>26630</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18598</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>35120</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20,93%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15423</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9784</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30507</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40893</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>45930</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>32052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56880</t>
+          <t>53246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
